--- a/public/templates/forms/A-048-ExternalConnectionInventory-FORM.xlsx
+++ b/public/templates/forms/A-048-ExternalConnectionInventory-FORM.xlsx
@@ -3,13 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Connections" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Relationships" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'External Connections'!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -17,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -197,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -262,6 +267,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -638,14 +646,14 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="27.75" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>« One row per external connection: ISP circuits, ESInet, cloud services, and vendor remote-access paths. Cross-system trusts and SAML federations go on the Trust Relationships tab. Reference vendors by name in the Vendor &amp; Contractor Inventory rather than restating them here. »</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>ID</t>
@@ -803,7 +811,6 @@
       <c r="B24" s="25" t="n"/>
       <c r="C24" s="13">
         <f>COUNTA(A12:A21)</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -815,7 +822,6 @@
       <c r="B25" s="25" t="n"/>
       <c r="C25" s="13">
         <f>COUNTIF(F12:F21,"Y*")</f>
-        <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -827,7 +833,6 @@
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="13">
         <f>COUNTIF(F12:F21,"N*")</f>
-        <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
@@ -839,7 +844,6 @@
       <c r="B27" s="25" t="n"/>
       <c r="C27" s="13">
         <f>COUNTIF(H12:H21,"&lt;"&amp;(TODAY()-365))</f>
-        <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -1010,7 +1014,7 @@
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="12" t="n"/>
     </row>
-    <row r="47" ht="30" customHeight="1">
+    <row r="47" ht="66.4" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Drafter's note (internal, delete before publishing): the connection register (this tab) lists every external connection with its protecting control and monitoring; the Trust Relationships tab carries cross-system trusts and SAML federations (assessment 2C-1). Vendors are recorded in the Vendor &amp; Contractor Inventory and referenced, not duplicated (assessment 11B-1). CJIS §5.1 and IC 36-8-16.7 apply only where an IDACS or other CJIS-regulated interconnection is listed. Agency-supplied values in brackets.</t>
@@ -1057,7 +1061,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1092,14 +1096,14 @@
       <c r="F1" s="10" t="n"/>
       <c r="G1" s="10" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="34.7" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>« One row per cross-system trust: SAML federations, certificate trusts, and API trusts. Record the systems, the trust type and direction, and the business justification. »</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="34.7" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Trust ID</t>
@@ -1231,8 +1235,8 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1240,7 +1244,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
@@ -1258,14 +1262,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="43.5" customHeight="1">
+    <row r="2" ht="161.4" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>How to use this template: fill the header block on the Register tab, replace every [BRACKETED] field, list one row per in-scope system or endpoint group, then delete every « » note before publishing.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="129.7" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, Source Authority, signatures and revision history live on the Register tab.</t>
@@ -1323,7 +1327,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="34.7" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Connection Type</t>
@@ -1389,7 +1393,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Protecting Control</t>
@@ -1411,7 +1415,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Monitored? (Y/N + how)</t>
@@ -1433,7 +1437,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Owner (Role)</t>
@@ -1455,7 +1459,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Last Verified</t>
@@ -1471,10 +1475,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+      <c r="D14" s="26">
+        <v>46082</v>
       </c>
     </row>
     <row r="15" ht="29.75" customHeight="1">
@@ -1492,7 +1494,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="18" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="119.2" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
           <t>« The Trust Relationships tab records cross-system trusts and SAML federations: the systems in the trust, the trust type and direction, and the justification. »</t>
@@ -1511,7 +1513,7 @@
       </c>
       <c r="B20" s="21" t="n"/>
     </row>
-    <row r="21" ht="42" customHeight="1">
+    <row r="21" ht="104.6" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
           <t>What minimum-viable upkeep looks like at each PSAP size. Keep all three rows while this ships as a template; once adopted, keep the one that fits.</t>
@@ -1531,7 +1533,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="66.4" customHeight="1">
       <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Small (1–5, no in-house IT)</t>
@@ -1543,7 +1545,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="50.5" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Medium (6–25, shared county IT)</t>
@@ -1555,7 +1557,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="50.5" customHeight="1">
       <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Large (25+, dedicated IT/security)</t>
@@ -1569,6 +1571,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>